--- a/LoanOfficer-A/2023/155 denita.xlsx
+++ b/LoanOfficer-A/2023/155 denita.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD20000.18-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="G2" s="21">
         <f>B3+G1-1</f>
-        <v>119</v>
+        <v>46138</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>12000</v>
+        <v>11600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -862,9 +862,15 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="3">
+        <v>46019</v>
+      </c>
+      <c r="C3" s="4">
+        <v>100</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
       <c r="E3" s="1">
         <v>31</v>
       </c>
@@ -888,9 +894,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>46019</v>
+      </c>
+      <c r="C4" s="4">
+        <v>100</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -914,9 +926,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>46019</v>
+      </c>
+      <c r="C5" s="4">
+        <v>100</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -940,9 +958,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>46019</v>
+      </c>
+      <c r="C6" s="4">
+        <v>100</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
